--- a/data/trans_dic/IP31KM05_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM05_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,55; 93,87</t>
+          <t>76,38; 91,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,55; 90,91</t>
+          <t>79,51; 94,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,75; 90,68</t>
+          <t>81,23; 91,33</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,35%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,74; 86,16</t>
+          <t>79,62; 88,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,61; 88,71</t>
+          <t>76,04; 86,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,29; 86,55</t>
+          <t>79,7; 86,48</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,28; 85,74</t>
+          <t>77,06; 87,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,88; 86,12</t>
+          <t>75,9; 85,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,83; 84,72</t>
+          <t>78,41; 85,32</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,34; 85,63</t>
+          <t>76,14; 85,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,43; 84,46</t>
+          <t>71,72; 81,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,33; 82,9</t>
+          <t>74,98; 81,91</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,47; 83,75</t>
+          <t>79,69; 84,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,52; 84,14</t>
+          <t>77,33; 82,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,07; 83,23</t>
+          <t>79,42; 83,23</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40767</t>
+          <t>31989</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>37803</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78450</t>
+          <t>69791</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36522; 43645</t>
+          <t>28594; 34298</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32856; 41167</t>
+          <t>33937; 40202</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72275; 83228</t>
+          <t>65077; 73172</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>209</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>130168</t>
+          <t>133210</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>154039</t>
+          <t>118984</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>284208</t>
+          <t>252193</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>120646; 137258</t>
+          <t>125034; 139692</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>144855; 161411</t>
+          <t>110652; 125260</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>270601; 295371</t>
+          <t>241150; 261645</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>189</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>139809</t>
+          <t>164843</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>172484</t>
+          <t>142761</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312295</t>
+          <t>307604</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>128556; 148386</t>
+          <t>154212; 174267</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>159105; 183005</t>
+          <t>132585; 150070</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>296209; 326656</t>
+          <t>293878; 319793</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>263</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>215532</t>
+          <t>235969</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>244553</t>
+          <t>195807</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>460085</t>
+          <t>431777</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>201147; 234867</t>
+          <t>222487; 250010</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>227010; 257600</t>
+          <t>183118; 207048</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>436379; 480240</t>
+          <t>410538; 448524</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>734</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>526278</t>
+          <t>566010</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>608760</t>
+          <t>495355</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1135038</t>
+          <t>1061364</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>506008; 547004</t>
+          <t>547310; 583530</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>584740; 626642</t>
+          <t>478057; 510739</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1105313; 1163495</t>
+          <t>1036479; 1086227</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM05_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM05_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que consumen pescados con regularidad (por lo menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>85,45%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>88,57%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>87,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>76,38; 91,62</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>79,51; 94,19</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>81,23; 91,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>84,82%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>81,77%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>83,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>79,62; 88,95</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>76,04; 86,08</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>79,7; 86,48</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>82,37%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>81,73%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>82,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>77,06; 87,08</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>75,9; 85,92</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>78,41; 85,32</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>80,75%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>76,69%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>78,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>76,14; 85,56</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>71,72; 81,09</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>74,98; 81,91</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>80,13%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>81,33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>79,69; 84,96</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>77,33; 82,62</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>79,42; 83,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8545088463139583</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.8857018088836529</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.871126510991269</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>31989</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>37803</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>69791</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7638197075010417</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.7951233229890212</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8122891697925868</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>28594; 34298</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>33937; 40202</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>65077; 73172</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9161948388746336</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9419127646112525</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9133212711338974</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.8482412446374423</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8176572727238475</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8335317242740822</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>133210</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>118984</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>252193</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.7961808059341799</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.7604004763054069</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.7970306667882806</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>125034; 139692</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>110652; 125260</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>241150; 261645</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.8895175027279321</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.8607879256097047</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.8647694961914861</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.8236940885630497</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.817309036451034</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8207183755671931</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>164843</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>142761</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>307604</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.7705731228751279</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.7590492313433115</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.7840979362480158</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>154212; 174267</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>132585; 150070</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>293878; 319793</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8707859977189133</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.8591550464111015</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8532412355952842</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8075033932900192</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.7668577148497472</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.788549507051576</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>235969</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>195807</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>431777</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.7613669899913161</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.7171634937813832</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.7497615180386767</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>222487; 250010</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>183118; 207048</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>410538; 448524</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8555509712551013</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.8108818260672253</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8191358705172554</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>734</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1506</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.824097730611566</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8012749870382651</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8132863464772361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>566010</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>495355</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1061364</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.7968715016082131</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.7732946395301733</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.7942181017584944</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>547310; 583530</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>478057; 510739</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1036479; 1086227</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.8496062956783793</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8261601407413717</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.8323378662793819</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumen pescados con regularidad (por lo menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>31989</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>37803</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>69791</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>28594</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>33937</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>65077</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>34298</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>40202</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>73172</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>232</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>209</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>133210</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>118984</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>252193</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>125034</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>110652</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>241150</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>139692</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>125260</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>261645</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>189</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>164843</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>142761</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>307604</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>154212</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>132585</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>293878</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>174267</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>150070</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>319793</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>272</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>235969</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>195807</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>431777</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>222487</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>183118</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>410538</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>250010</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>207048</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>448524</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>772</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>566010</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>495355</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1061364</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>547310</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>478057</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1036479</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>583530</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>510739</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1086227</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>